--- a/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/ssks_vorlage.xlsx
+++ b/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/ssks_vorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_intern\planpro\set\java\bundles\org.eclipse.set.feature\rootdir\data\export\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE9C706E-3728-446F-8EEA-BFDDA5EC72FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EAB46F-80DA-4EB0-A5F6-6F3572689794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ssks_Beispielbefüllung" sheetId="2" r:id="rId1"/>
@@ -608,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -697,46 +697,34 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1112,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AY557"/>
+  <dimension ref="B1:AY557"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="1.5703125" defaultRowHeight="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="16" customWidth="1"/>
@@ -1156,32 +1144,32 @@
     <col min="52" max="16384" width="1.5703125" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="4" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="2:51" s="4" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1190,195 +1178,193 @@
       <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="31" t="s">
+      <c r="Q1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="30" t="s">
         <v>17</v>
       </c>
       <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="31" t="s">
+      <c r="V1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="31" t="s">
+      <c r="W1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="31" t="s">
+      <c r="X1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="31" t="s">
+      <c r="Y1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="31" t="s">
+      <c r="Z1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="31" t="s">
+      <c r="AA1" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="31" t="s">
+      <c r="AB1" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="31" t="s">
+      <c r="AC1" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="31" t="s">
+      <c r="AD1" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="31" t="s">
+      <c r="AE1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="31" t="s">
+      <c r="AF1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="31" t="s">
+      <c r="AG1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="31" t="s">
+      <c r="AH1" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="31" t="s">
+      <c r="AI1" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="31" t="s">
+      <c r="AJ1" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="31" t="s">
+      <c r="AK1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="31" t="s">
+      <c r="AL1" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="31" t="s">
+      <c r="AM1" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="31" t="s">
+      <c r="AN1" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="31" t="s">
+      <c r="AO1" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="31" t="s">
+      <c r="AP1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="31" t="s">
+      <c r="AQ1" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="31" t="s">
+      <c r="AR1" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="31" t="s">
+      <c r="AS1" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="31" t="s">
+      <c r="AT1" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="31" t="s">
+      <c r="AU1" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="31" t="s">
+      <c r="AV1" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="31" t="s">
+      <c r="AW1" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="31" t="s">
+      <c r="AX1" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="AY1" s="31" t="s">
+      <c r="AY1" s="30" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:51" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30"/>
+    <row r="2" spans="2:51" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="41" t="s">
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="41" t="s">
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="41" t="s">
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="41" t="s">
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="37"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="42"/>
-      <c r="AK2" s="42"/>
-      <c r="AL2" s="42"/>
-      <c r="AM2" s="42"/>
-      <c r="AN2" s="42"/>
-      <c r="AO2" s="42"/>
-      <c r="AP2" s="42"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="41" t="s">
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="37"/>
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="37"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="37"/>
+      <c r="AO2" s="37"/>
+      <c r="AP2" s="37"/>
+      <c r="AQ2" s="38"/>
+      <c r="AR2" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="AS2" s="42"/>
-      <c r="AT2" s="42"/>
-      <c r="AU2" s="42"/>
-      <c r="AV2" s="42"/>
-      <c r="AW2" s="42"/>
-      <c r="AX2" s="43"/>
+      <c r="AS2" s="37"/>
+      <c r="AT2" s="37"/>
+      <c r="AU2" s="37"/>
+      <c r="AV2" s="37"/>
+      <c r="AW2" s="37"/>
+      <c r="AX2" s="38"/>
       <c r="AY2" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:51" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
+    <row r="3" spans="2:51" s="4" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
         <v>54</v>
@@ -1389,10 +1375,10 @@
       <c r="E3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="36" t="s">
+      <c r="F3" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="35"/>
+      <c r="G3" s="31"/>
       <c r="H3" s="5" t="s">
         <v>57</v>
       </c>
@@ -1402,60 +1388,60 @@
       <c r="J3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="35" t="s">
+      <c r="K3" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35" t="s">
+      <c r="L3" s="31"/>
+      <c r="M3" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35" t="s">
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="36" t="s">
+      <c r="Q3" s="32"/>
+      <c r="R3" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="S3" s="35"/>
+      <c r="S3" s="31"/>
       <c r="T3" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="U3" s="35" t="s">
+      <c r="U3" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="V3" s="35"/>
-      <c r="W3" s="35" t="s">
+      <c r="V3" s="31"/>
+      <c r="W3" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="36" t="s">
+      <c r="X3" s="32"/>
+      <c r="Y3" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="Z3" s="35"/>
+      <c r="Z3" s="31"/>
       <c r="AA3" s="5" t="s">
         <v>93</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AC3" s="36" t="s">
+      <c r="AC3" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="35"/>
-      <c r="AF3" s="35"/>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35" t="s">
+      <c r="AD3" s="31"/>
+      <c r="AE3" s="31"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="35"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
       <c r="AO3" s="5" t="s">
         <v>111</v>
       </c>
@@ -1480,14 +1466,13 @@
       <c r="AV3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="AW3" s="35" t="s">
+      <c r="AW3" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="AX3" s="37"/>
+      <c r="AX3" s="32"/>
       <c r="AY3" s="25"/>
     </row>
-    <row r="4" spans="1:51" s="4" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
+    <row r="4" spans="2:51" s="4" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="5"/>
@@ -1605,8 +1590,7 @@
       </c>
       <c r="AY4" s="18"/>
     </row>
-    <row r="5" spans="1:51" s="4" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
+    <row r="5" spans="2:51" s="4" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
       <c r="D5" s="13"/>
@@ -1678,59 +1662,59 @@
       <c r="AX5" s="14"/>
       <c r="AY5" s="24"/>
     </row>
-    <row r="6" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="32"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="34"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30"/>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30"/>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30"/>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
-      <c r="AW6" s="30"/>
-      <c r="AX6" s="30"/>
-      <c r="AY6" s="32"/>
+    <row r="6" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="27"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AF6" s="4"/>
+      <c r="AG6" s="4"/>
+      <c r="AH6" s="4"/>
+      <c r="AI6" s="4"/>
+      <c r="AJ6" s="4"/>
+      <c r="AK6" s="4"/>
+      <c r="AL6" s="4"/>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4"/>
+      <c r="AP6" s="4"/>
+      <c r="AQ6" s="4"/>
+      <c r="AR6" s="4"/>
+      <c r="AS6" s="4"/>
+      <c r="AT6" s="4"/>
+      <c r="AU6" s="4"/>
+      <c r="AV6" s="4"/>
+      <c r="AW6" s="4"/>
+      <c r="AX6" s="4"/>
+      <c r="AY6" s="27"/>
     </row>
-    <row r="7" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="27"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -1782,63 +1766,63 @@
       <c r="AX7" s="4"/>
       <c r="AY7" s="27"/>
     </row>
-    <row r="8" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
       <c r="T8" s="16"/>
       <c r="AY8" s="16"/>
     </row>
-    <row r="9" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="T9" s="16"/>
       <c r="AY9" s="16"/>
     </row>
-    <row r="10" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
       <c r="T10" s="16"/>
       <c r="AY10" s="16"/>
     </row>
-    <row r="11" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="16"/>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
       <c r="T11" s="16"/>
       <c r="AY11" s="16"/>
     </row>
-    <row r="12" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="16"/>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
       <c r="T12" s="16"/>
       <c r="AY12" s="16"/>
     </row>
-    <row r="13" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="16"/>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
       <c r="T13" s="16"/>
       <c r="AY13" s="16"/>
     </row>
-    <row r="14" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="16"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="T14" s="16"/>
       <c r="AY14" s="16"/>
     </row>
-    <row r="15" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="16"/>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
       <c r="T15" s="16"/>
       <c r="AY15" s="16"/>
     </row>
-    <row r="16" spans="1:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:51" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="16"/>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
@@ -2388,6 +2372,7 @@
     <row r="557" s="16" customFormat="1" ht="10.15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="M3:O3"/>
     <mergeCell ref="AW3:AX3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="C2:E2"/>
@@ -2404,7 +2389,6 @@
     <mergeCell ref="AH3:AN3"/>
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="M3:O3"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.19685039370078741" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -2416,6 +2400,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100E758A0F93049BE4CAD441F10C0D8186D" ma:contentTypeVersion="5" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="fb340e34ecc5d059b634082484788e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="576ce185-3b2e-4f75-8b7c-efeb82226bea" xmlns:ns3="http://schemas.microsoft.com/sharepoint/v3/fields" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae5cd419a40dc0c21009e0c04d2bd83e" ns2:_="" ns3:_="">
     <xsd:import namespace="576ce185-3b2e-4f75-8b7c-efeb82226bea"/>
@@ -2607,20 +2600,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -2666,7 +2646,19 @@
 </spe:Receivers>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F25B32D-FD26-4105-AE41-4DDE11D43643}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5CD9C34-55B9-46DF-94B7-6C19782F39DF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2685,26 +2677,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F25B32D-FD26-4105-AE41-4DDE11D43643}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5608CC1-62E8-40C3-93D3-D4A0440D7ADA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E76690F-8A23-45F3-AC2B-ADA60E406AB9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5608CC1-62E8-40C3-93D3-D4A0440D7ADA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/events"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>